--- a/www/download/COUNTRY.HUN.EXI382.xlsx
+++ b/www/download/COUNTRY.HUN.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Hungria</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.9456</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4.667</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.801</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>3.703</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3.661</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>3.726</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3.855</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3.813</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>3.963</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>3.792</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4.028</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>3.993</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>3.924</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>4.033</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>4.027</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>3.809</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>3.782</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>3.81</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>3.876</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>3.795</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>3.804</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4.023</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>3.982</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>4.298</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>4.599</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>4.77</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>4.887</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4.061</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3.141</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3.047</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3.025</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>3.132</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3.251</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3.238</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>3.387</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>3.266</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>3.493</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>3.418</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>3.383</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>3.523</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>3.529</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>3.338</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>3.316</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>3.351</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>3.423</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>3.352</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>3.349</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>3.504</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>3.778</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>4.042</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>4.185</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>4.275</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>9311.948</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>8185.946</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>7983.327</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>8036.327</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>8085.717</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>8454.505</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>8164.336</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>8547.169</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>8192.971</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>8569.793</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>8503.135</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>8269.235</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>8475.125</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>8401.981</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>7955.018</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>7829.646</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>7816.867</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>7802.694</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>7820.09</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>7642.752</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>7644.57</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8060.176</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>7959.893</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>8556.384</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>9133.616</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>9462.556</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>9670.951</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9249.801</t>
+          <t>18310731654.9824</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7903.516</t>
+          <t>16795341948.0362</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7699.552</t>
+          <t>15227007788.2012</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7770.26</t>
+          <t>16360484523.5691</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7873.157</t>
+          <t>17907196107.3889</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8196.551</t>
+          <t>17759498954.5712</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7879.036</t>
+          <t>19500010778.2296</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8328.109</t>
+          <t>19647843639.5391</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7971.619</t>
+          <t>19338430102.1065</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>8322.943</t>
+          <t>20773840706.4628</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>8283.253</t>
+          <t>20739909581.7629</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>8103.059</t>
+          <t>19966914657.5585</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>8400.355</t>
+          <t>18877962453.4454</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>8334.356</t>
+          <t>20238244554.6394</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>7886.61</t>
+          <t>17110014606.8953</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>7706.64</t>
+          <t>17122944226.9701</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>7726.319</t>
+          <t>17288107830.5803</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>7691.758</t>
+          <t>15614022294.8888</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>7739.7</t>
+          <t>15647911592.7593</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>7602.732</t>
+          <t>15303668727.157</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>7602.527</t>
+          <t>15389269738.8863</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>8015.414</t>
+          <t>16687834624.9416</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>7915.241</t>
+          <t>16703121989.8765</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>8506.673</t>
+          <t>18965115157.902</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>9079.161</t>
+          <t>18833536893.8957</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>9404.711</t>
+          <t>20507689961.6555</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>9610.98</t>
+          <t>20358869065.6776</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3757200156.51844</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3144826093.13967</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2674085192.0245</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2852248954.61968</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2929445310.62033</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2842838309.32843</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3136754208.02288</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2833455116.7512</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3196803880.38325</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>3431856990.55023</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3274821773.8631</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2906702689.31729</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2851672660.8222</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3215845860.64325</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2770750907.45892</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2336990819.53349</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2556466892.4045</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2276082741.14351</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2226792757.17743</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2316742510.82666</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2334647839.44778</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2434726706.61303</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2502157823.33006</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>2715064923.33254</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2810980490.09173</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>3209227272.43524</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3090356482.54149</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>48974535.8036535</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>41194172.0647119</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>32659858.2961127</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>32172497.3420514</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>32328746.4925315</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>27441431.7223058</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>26062511.7088758</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>19970235.8895007</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>22093378.4403832</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>20428857.9851993</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>16845194.4715057</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>16458115.1783814</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>12834576.8610696</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>13357399.0867363</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>14036004.2604374</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>11157245.0292318</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>12742860.6725162</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>13072103.0332472</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>10738328.9201497</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2225506149.68159</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2159912928.67962</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2245454485.13835</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2147782463.76832</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>9082117.14880661</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>8639825.83599429</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>8984771.39911832</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>8657685.60302599</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20851.8868364678</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>39966.250517876</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>42792.0902779671</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>43732.5796874667</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>46900.9420654915</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>57317.7824972456</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>56491.0480482764</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>56174.9732677822</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>49627.0814994879</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>49445.7840590028</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>52633.0268443952</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>52787.6069292395</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>56936.7656526323</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>56487.5971116969</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>52558.4871800852</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>59935.9597726381</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>62190.5700987758</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>69056.1388297827</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>66974.7185700693</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>69187.7367035911</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>77908.7099633129</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>75302.5192763346</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>78758.2150239344</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>82698.8335499091</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>95616.2825488183</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>94280.0363384966</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>95032.6605846756</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>68255.1316855786</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>127629.019943488</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>126028.218395047</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>139210.397884084</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>160722.364937864</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>190538.351595413</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>210068.770011072</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>205175.293255968</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>185509.335513763</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>194742.744949168</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>208431.357963917</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>214650.520343544</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>210261.08736441</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>226496.506776922</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>191891.364956256</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>221457.197426431</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>232772.45644355</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>232045.436423754</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>227160.407879635</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>229956.58139131</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>261219.728908129</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>258184.794923054</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>273214.480508623</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>301705.675295824</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>319226.015860074</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>330675.365351662</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>322294.337444631</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.4618867877512</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.51318062300534</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.87932187910981</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1.72425728736456</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1.6875930987534</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.88322799545234</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.51184360567589</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.93920625414703</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.49362153522001</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.42520099844398</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.52937520634215</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.78771510749317</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.94576411781356</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1.59165282204584</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.84638001155864</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2.29767662567827</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2.02226444745116</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2.37938417657712</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2.47571635261168</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2.28164746169196</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2.25639147748874</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2.29212058076555</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2.16336603372786</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>2.1331380988143</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2.22989104112755</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1.93052183371712</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2.10999086947735</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>925.152371336364</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1001.12249487167</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>877.526069643351</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>943.016912854165</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>935.267642749326</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>874.369731900532</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>968.672166025286</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>836.617195214339</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>978.693326103038</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>982.411184424371</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>958.082494328486</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>859.183201595368</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>809.329547558517</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>911.288464009455</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>829.988589239347</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>706.103519815523</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>770.832773226394</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>679.306017174313</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>650.614374211842</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>691.12950174046</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>697.196065699983</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>687.704147150743</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>714.078260804196</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>718.70239569159</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>695.461363432497</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>766.928940408163</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>722.914326296163</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1351652655.16851</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>341085775.425569</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-188640902.387232</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-401891005.249169</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-326280394.462363</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-660780751.186633</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-286346231.183446</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>-77950069.5073662</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>284474524.788986</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>246398011.178682</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>355592497.58734</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>-147212885.423256</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>-475399965.772835</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>-329315395.605986</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>324138581.934464</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-77890997.4148192</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>-26267177.6208217</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-119713866.56172</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>-101002353.258447</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>-61463125.1159894</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>-20132310.0741345</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>44524067.2836776</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>-248706960.838279</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>-417750612.348255</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>-148552570.887176</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>-127363240.162512</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>-655448492.357116</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1867766750.60439</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>349402246.993687</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-30567603.7643354</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-195760094.915993</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-20792384.7119992</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-374556351.881058</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-39675580.5623797</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>212659775.246658</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>663711222.4957</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>742251853.688573</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>678297110.871967</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>170952361.177131</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-161487439.036736</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>-164098530.206477</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>378299071.618287</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-90177506.7277563</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>61963561.9509617</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>-47336610.5478047</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>-60511283.8039643</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-170214759.742665</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-188520011.95946</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-223851387.316786</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>-510315486.977346</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>-695373209.322837</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-483424969.721904</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-559243986.294072</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>496570958.319779</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-516114095.435886</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-8316471.5681189</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-158073298.622897</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-206130910.333176</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-305488009.750364</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-286224399.305574</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-246670650.621067</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-290609844.754025</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-379236697.706714</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-495853842.509891</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-322704613.284627</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-318165246.600388</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-313912526.736099</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-165216865.39951</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-54160489.6838234</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>12286509.3129372</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-88230739.5717835</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-72377256.013915</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-40491069.4544832</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>108751634.626675</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>168387701.885325</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>268375454.600463</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>261608526.139067</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>277622596.974582</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>334872398.834728</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>431880746.13156</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-1152019450.6769</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>2277.62039964969</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>2516.00165536625</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>2526.68001181334</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>2569.02069695099</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>2513.61886214045</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>2521.00728939177</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>2433.15298622683</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>2458.99049250093</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>2440.49075434664</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2382.54458534852</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>2423.35010678492</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>2395.15799119176</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>2384.09394068416</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>2361.74331944792</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>2362.46293023263</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>2328.50107260481</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>2329.66048545231</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>2295.6360054925</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>2261.35101969231</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>2268.04337508701</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>2270.3433264841</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>2264.00497631278</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>2258.89091565146</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>2251.79385765043</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>2246.26442720097</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>2247.50200477566</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>2248.25695419544</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1995.12150674971</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>2153.85623322681</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>2156.08258838111</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>2195.1180005458</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>2170.13795324524</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>2193.07021867125</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2141.24052558415</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>2156.52444870614</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>2160.4226986256</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>2127.39691681306</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>2129.40373635207</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>2107.45578265989</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>2101.39222930264</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>2086.56741252139</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>2088.31491350016</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>2070.2395557907</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>2067.7901224776</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>2047.84368274712</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>2017.72324999332</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>2013.69545661567</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>2009.48823114175</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>2003.36917383423</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>1998.83096585069</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1990.62512330792</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>1985.85084130712</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1983.75250007268</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>1979.06483990389</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>14587.1327943089</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>15534.9590630139</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>21365.8409244118</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>25216.1879669024</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>28611.1632584333</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>38438.4117214802</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>44123.8022881256</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>47317.5492610232</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>46414.8535697364</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>54715.1801158207</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>61592.7165761921</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>72890.615373347</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>85832.8424941158</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>87998.9280649968</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>75594.4717082039</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>87163.2176273993</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>93305.3584984502</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>93086.6636972754</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>93778.5061711713</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>100454.170437255</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>113514.005458139</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>116606.322107646</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>125159.907149424</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>128996.585315403</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>136918.845539047</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>145393.803691455</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>152273.985512807</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3993665483.15544</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3605603942.92409</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3668349928.54802</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>4085687592.8274</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>4744149503.54679</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>5167683903.0281</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6097612030.81015</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>5980791547.86635</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>5753292404.14646</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>6367845411.42245</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>6499101229.01977</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>7230705577.77334</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>7321330071.18043</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>7785164038.99451</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>6551636509.83628</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>7154027410.27171</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>7250507782.82074</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>6588337897.20298</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>6569387049.08888</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>6354085088.60105</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>6634204635.71478</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>7477939284.14795</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>7589060848.10816</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>8388857277.22456</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>8167246887.11197</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>9079609378.95704</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>8881756785.22709</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>14590.729366706</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>15307.4271896509</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>20840.9650161163</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>26108.100439152</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>30260.4076936769</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>40906.4863723264</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>45136.7844642077</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>49230.9457834574</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>50300.902387904</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>59042.9682152765</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>64334.1739500233</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>74250.7507397266</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>85114.5733637798</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>87498.1102327092</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>70651.3342153358</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>80310.3276906888</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>85194.1792129839</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>84248.751311014</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>84454.4822086163</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>91671.7291402096</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>101787.589163043</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>103425.448053846</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>113862.884316929</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>121174.005386412</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>130962.445408712</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>142000.199853237</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>150967.397077135</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9311.948</t>
+          <t>5347355690.95988</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8185.946</t>
+          <t>3900469337.55104</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7983.327</t>
+          <t>3381458703.08071</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>8036.327</t>
+          <t>3851831399.40668</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8085.717</t>
+          <t>4720412928.55706</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8454.505</t>
+          <t>4889801680.66118</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8164.336</t>
+          <t>5974638540.41265</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8547.169</t>
+          <t>6223016912.44688</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8192.971</t>
+          <t>6697919797.51671</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8569.793</t>
+          <t>7407915796.85371</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>8503.135</t>
+          <t>7313204074.25976</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>8269.235</t>
+          <t>7285869545.19176</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>8475.125</t>
+          <t>6756733718.07052</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>8401.981</t>
+          <t>7387216893.46029</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>7955.018</t>
+          <t>6148187714.44894</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>7829.646</t>
+          <t>6231161265.59771</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>7816.867</t>
+          <t>6288893839.46603</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>7802.694</t>
+          <t>5505015558.88078</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>7820.09</t>
+          <t>5400284587.1561</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>7642.752</t>
+          <t>5358994946.22054</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>7644.57</t>
+          <t>5480539661.74929</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>8060.176</t>
+          <t>6124545563.9704</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>7959.893</t>
+          <t>6252193501.8915</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>8556.384</t>
+          <t>7193622744.36064</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>9133.616</t>
+          <t>7475069126.64992</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>9462.556</t>
+          <t>8622926320.96557</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>9670.951</t>
+          <t>8099000751.97116</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9249.801</t>
+          <t>-3.59657239709156</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7903.516</t>
+          <t>227.531873363007</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7699.552</t>
+          <t>524.875908295453</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7770.26</t>
+          <t>-891.912472249544</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7873.157</t>
+          <t>-1649.2444352436</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8196.551</t>
+          <t>-2468.07465084626</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7879.036</t>
+          <t>-1012.98217608213</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8328.109</t>
+          <t>-1913.39652243415</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7971.619</t>
+          <t>-3886.04881816758</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>8322.943</t>
+          <t>-4327.78809945582</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>8283.253</t>
+          <t>-2741.45737383125</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>8103.059</t>
+          <t>-1360.13536637966</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>8400.355</t>
+          <t>718.269130336003</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>8334.356</t>
+          <t>500.817832287661</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>7886.61</t>
+          <t>4943.13749286811</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>7706.64</t>
+          <t>6852.88993671053</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>7726.319</t>
+          <t>8111.17928546637</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>7691.758</t>
+          <t>8837.91238626143</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>7739.7</t>
+          <t>9324.02396255492</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>7602.732</t>
+          <t>8782.44129704571</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>7602.527</t>
+          <t>11726.4162950964</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>8015.414</t>
+          <t>13180.8740538004</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>7915.241</t>
+          <t>11297.0228324947</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>8506.673</t>
+          <t>7822.57992899127</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>9079.161</t>
+          <t>5956.40013033442</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>9404.711</t>
+          <t>3393.6038382177</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>9610.98</t>
+          <t>1306.58843567161</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10416.59</t>
+          <t>-1353690207.80444</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9595.055</t>
+          <t>-294865394.626951</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8965.09</t>
+          <t>286891225.467315</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>9529.591</t>
+          <t>233856193.420712</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>10323.711</t>
+          <t>23736574.9897327</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>10334.353</t>
+          <t>277882222.366919</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11159.258</t>
+          <t>122973490.397497</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>11415.803</t>
+          <t>-242225364.580527</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>11228.459</t>
+          <t>-944627393.370254</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>11976.54</t>
+          <t>-1040070385.43126</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>11928.654</t>
+          <t>-814102845.239992</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>11532.048</t>
+          <t>-55163967.4184157</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>11159.392</t>
+          <t>564596353.109915</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>11853.707</t>
+          <t>397947145.534223</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>10228.601</t>
+          <t>403448795.387333</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>10160.378</t>
+          <t>922866144.673993</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>10245.671</t>
+          <t>961613943.354707</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>9375.832</t>
+          <t>1083322338.32219</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>9385.502</t>
+          <t>1169102461.93278</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>9146.515</t>
+          <t>995090142.380511</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>9229.367</t>
+          <t>1153664973.96549</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>9963.489</t>
+          <t>1353393720.17754</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>10042.375</t>
+          <t>1336867346.21666</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11319.22</t>
+          <t>1195234532.86392</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>11391.021</t>
+          <t>692177760.462051</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12323.192</t>
+          <t>456683057.991473</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>12266.532</t>
+          <t>782756033.25593</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>11230.4668110963</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>12092.4906490958</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>13021.6206312855</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>13581.056962053</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>14008.9193746496</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>16662.3879413768</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>19302.4957725498</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>20582.446189494</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>22949.3010543594</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>25614.6410308757</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>26727.8539087169</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>27910.5873056467</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>31408.2919534806</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>31708.3183280146</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>29450.5243907673</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>29839.9938092526</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>30376.0999287559</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>29804.4578607328</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>30649.2598643517</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>31489.0102242843</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>33991.6621902933</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>33486.4740919556</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>37752.7085465474</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>43135.2764035832</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>43619.7673745282</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>46072.4922840145</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>47059.6852924199</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>5593.914</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>5259.359</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>5170.235</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>5139.603</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>5225.56</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>5342.416</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5243.883</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>5379.386</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>5173.378</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>5274.542</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>5237.236</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>4910.334</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>5111.978</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>5047.362</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>4686.383</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>4634.214</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>4618.92</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>4646.694</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>4613.544</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>4604.461</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>4589.845</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>4867.196</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>4814.928</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>5198.42</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>5641.122</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>5847.021</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>6003.076</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>16182.9572842615</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>17219.4023329625</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>18474.8539456442</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>19675.9002115117</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>20120.3035705146</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>22529.0115783358</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>28542.4767724727</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>30553.8588942691</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>35564.7396853465</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>39386.146508755</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>42134.7589433616</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>43873.9016577257</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>48581.9463915817</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>51568.4862798301</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46146.3839761602</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>47050.1323470546</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>49082.6197287359</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>47197.3214147598</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>48773.947297842</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>50855.108779853</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>54193.6142144632</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>55630.4955519315</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>58854.9216126456</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>68418.4769752945</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>70880.6860637712</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>76590.7226063639</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78275.0183680865</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>3465.501</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2645.933</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2367.264</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2488.202</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2539.219</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2502.38</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2697.74</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2514.747</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>2811.638</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>2994.729</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2839.308</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>2562.209</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>2567.474</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>2840.99</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>2515.667</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>2114.288</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>2334.537</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2099.794</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>2019.154</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>2146.843</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>2131.033</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>2262.37</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2365.077</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>2498.11</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2692.519</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>3141.977</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>2909.885</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>166.91</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>198.7</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>225.25</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>212.28</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>210.06</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>227.55</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>192.06</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>231.17</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>183.52</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>177.92</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>191.73</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>216.25</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>227.18</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>193.36</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>213.5</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>264.5</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>230.96</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>266.31</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>283.31</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>254.14</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>256.75</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>254.29</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>234.67</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>240.52</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>237.2</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>199.32</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>230.29</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>36.29</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>31.254</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>25.654</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>25.552</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>25.061</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>21.845</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20.659</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>15.687</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>17.601</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>15.98</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>12.899</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>13.09</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>10.262</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>10.586</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>11.146</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>8.764</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>10.467</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>10.728</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>8.574</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>2102.942</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>2040.993</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>2121.741</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2029.392</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>7.199</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>6.911</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>7.099</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>6.823</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>16101.6454044722</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>15855.5956601633</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>18897.6602588405</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>19441.599344013</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>21125.1819527632</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>23129.3930726489</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>25601.2034293546</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>33653.5981518265</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>32136.3964914099</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>35121.2611987262</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>38931.3809228075</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>38648.7603039823</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>42373.5635920115</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>43734.1670117004</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>37225.9769620281</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>40480.5117559416</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>40899.3395076001</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>40615.6613445295</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>41009.5657509425</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>42639.9963455863</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>44878.2264384016</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>46708.9924433905</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>50037.0005066104</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>50130.8104341322</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>57015.0782201958</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>56221.2510608394</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>57453.3418053595</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>9249801424.26949</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>7903516000.00021</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>7699551999.9997</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>7770260000.0006</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>7873156999.9987</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>8196551000.00013</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7879035999.99921</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>8328109000.00005</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>7971618999.99858</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>8322942999.9994</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>8283252999.99875</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>8103059000.00083</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>8400354999.99996</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>8334356000.00052</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>7886609999.99904</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>7706640000.0003</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>7726319000.00005</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>7691758000.00065</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>7739699999.99885</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>7602732180.04816</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>7602527327.31525</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>8015413899.38027</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>7915241069.34876</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>8506673352.04753</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>9079160701.73161</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>9404710591.2319</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>9610980444.13418</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>9311948372.18986</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>8185946000.00026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>7983326999.99981</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8036327000.00058</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>8085716999.99872</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>8454505000.0001</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8164335999.9993</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>8547169000.00011</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>8192970999.99851</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>8569792999.99942</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>8503134999.9988</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>8269235000.0008</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>8475124999.99996</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>8401981000.00053</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>7955017999.99904</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>7829646000.00033</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>7816866999.99999</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>7802694000.00073</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>7820089999.99894</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>7642751941.05801</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>7644569589.98377</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>8060175804.30992</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>7959892867.19085</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>8556383992.18949</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>9133615735.06327</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>9462555936.28276</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>9670950888.0564</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5593913526.11359</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>5259359071.51702</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>5170234890.51896</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>5139603104.56345</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>5225560036.48117</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5342415790.91461</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5243882971.07091</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5379385956.78632</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5173377631.32784</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>5274542278.40936</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>5237236030.27252</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>4910333507.90836</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>5111978339.33083</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>5047361749.27597</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4686383275.10243</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>4634214233.28424</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>4618919688.09307</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>4646693802.32115</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>4613543728.49025</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>4604461399.1358</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>4589845329.2391</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>4867195951.25445</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>4814928077.02109</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>5198420282.15207</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>5641121636.6202</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>5847020847.00904</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>6003076284.69825</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4667359.02584707</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3800599.99999927</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3702700.00000049</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3661000.0000011</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3725900.00000105</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3855100.00000025</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3812899.99999977</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>3963399.99999917</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3792300.00000031</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4028300.00000065</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>3993199.99999893</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>3923799.99999997</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4033099.99999975</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4026700.00000031</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>3809300.00000139</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>3781999.99999995</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>3780299.999999</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>3810199.99999885</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>3875699.99999992</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>3795386.19702844</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>3804237.05474518</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>4023310.28628319</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>3982274.1408267</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>4298340.20077619</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>4599346.30792883</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>4770028.4868884</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>4886626.59911943</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>4061169.02785563</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3141299.99999929</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3047300.00000037</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3024600.00000103</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3132200.00000095</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3251300.00000026</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3238199.99999979</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3386799.99999914</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3266400.00000029</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3493300.00000059</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3418099.99999886</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3383100</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3523499.99999971</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3528900.00000032</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3338300.00000145</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>3309700.00000008</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>3316499.99999891</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>3350599.9999989</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>3422599.99999997</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>3352110.57405659</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>3348624.51798807</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>3540369.38224155</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>3504038.64768566</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>3777731.83950487</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>4041893.1056327</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>4184517.1088827</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>4274858.54150224</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>9311948372.18986</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8185946000.00026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>7983326999.99981</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8036327000.00058</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>8085716999.99872</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>8454505000.0001</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8164335999.9993</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>8547169000.00011</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>8192970999.99851</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>8569792999.99942</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>8503134999.9988</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>8269235000.0008</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>8475124999.99996</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>8401981000.00053</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7955017999.99904</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>7829646000.00033</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>7816866999.99999</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>7802694000.00073</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>7820089999.99894</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>7642751941.05801</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>7644569589.98377</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>8060175804.30992</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>7959892867.19085</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>8556383992.18949</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>9133615735.06327</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>9462555936.28276</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>9670950888.0564</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>9249801424.26949</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>7903516000.00021</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>7699551999.9997</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>7770260000.0006</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>7873156999.9987</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>8196551000.00013</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7879035999.99921</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>8328109000.00005</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>7971618999.99858</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>8322942999.9994</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>8283252999.99875</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>8103059000.00083</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>8400354999.99996</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>8334356000.00052</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>7886609999.99904</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>7706640000.0003</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>7726319000.00005</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>7691758000.00065</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>7739699999.99885</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>7602732180.04816</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>7602527327.31525</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>8015413899.38027</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>7915241069.34876</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>8506673352.04753</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>9079160701.73161</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>9404710591.2319</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>9610980444.13418</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>60279.4896582501</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>63151.9650009584</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>73652.8036842719</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>79481.4392778964</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>86884.8825566775</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>102052.036170477</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>118350.617722364</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>137983.578769567</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>143072.824477764</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>160650.240422115</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>176955.161166558</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>188294.58655651</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>209233.074775272</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>220835.149551272</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>181414.758953145</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>197528.222208231</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>207173.07245317</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>196062.737185524</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>197751.019641684</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>207227.013826615</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>222630.150519242</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>228396.590963669</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>245586.551198356</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>269669.07273587</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>282356.475586006</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>295207.486975839</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>303566.389428141</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>17470.5581967425</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>18893.1863402378</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>20541.4990627006</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>21640.503267145</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>22413.7388294894</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>25213.7531879348</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>31149.0714279044</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>33949.1950648368</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>39169.8153917607</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>43908.0633268092</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>46941.7676761457</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>48393.17484152</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>54198.3641729286</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>57934.096081321</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>51422.5548888028</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>53613.3688948527</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>55399.5064420902</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>53941.0255082769</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>55402.8298076972</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>57553.7574018931</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>61719.5607284224</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>63040.5215704731</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>69627.064626734</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>78312.9246891692</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>81061.1405702904</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>86411.4829497408</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>89315.7414914946</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
